--- a/artfynd/A 18717-2021 artfynd.xlsx
+++ b/artfynd/A 18717-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 18717-2021 artfynd.xlsx
+++ b/artfynd/A 18717-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>59562059</v>
+        <v>59562050</v>
       </c>
       <c r="B2" t="n">
-        <v>95519</v>
+        <v>95511</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>221944</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lopplummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Huperzia selago</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -793,6 +793,126 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>59562059</v>
+      </c>
+      <c r="B3" t="n">
+        <v>95519</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kavelbromossen V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>564522.0454735826</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6624135.214052881</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2016-05-14</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2016-05-14</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Kanten på skogsbäck, granskog, inslag av björk</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
